--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-20.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_2FF9329A54CAB55F779B2611595ED87656CD62AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07ABB48E-4856-46EF-9C5C-2A5C90D99599}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_2FF9329A54CAB55F779B2611595ED87656CD62AE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AF5DB1B-468E-4CFB-B5CA-F53EE2662715}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,9 +103,6 @@
     <t>LAY</t>
   </si>
   <si>
-    <t>vs</t>
-  </si>
-  <si>
     <t>PENDENTE</t>
   </si>
   <si>
@@ -656,6 +653,9 @@
   </si>
   <si>
     <t>3x1</t>
+  </si>
+  <si>
+    <t>2X3</t>
   </si>
 </sst>
 </file>
@@ -731,6 +731,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1118,13 +1122,16 @@
         <v>100</v>
       </c>
       <c r="N2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O2" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
       </c>
       <c r="R2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -1132,25 +1139,25 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>32</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>33</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
       </c>
       <c r="I3" t="s">
         <v>26</v>
@@ -1168,13 +1175,16 @@
         <v>100</v>
       </c>
       <c r="N3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O3" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -1182,25 +1192,25 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>40</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>41</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>42</v>
-      </c>
-      <c r="H4" t="s">
-        <v>43</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
@@ -1218,13 +1228,16 @@
         <v>100</v>
       </c>
       <c r="N4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -1232,25 +1245,25 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>46</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>47</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>49</v>
-      </c>
-      <c r="H5" t="s">
-        <v>50</v>
       </c>
       <c r="I5" t="s">
         <v>26</v>
@@ -1268,13 +1281,16 @@
         <v>100</v>
       </c>
       <c r="N5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O5" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -1282,25 +1298,25 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
         <v>51</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>54</v>
       </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
       <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
         <v>35</v>
-      </c>
-      <c r="H6" t="s">
-        <v>36</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
@@ -1318,13 +1334,16 @@
         <v>100</v>
       </c>
       <c r="N6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O6" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -1332,25 +1351,25 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
         <v>51</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>52</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>53</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>54</v>
       </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
       <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
         <v>49</v>
-      </c>
-      <c r="H7" t="s">
-        <v>50</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
@@ -1368,13 +1387,16 @@
         <v>100</v>
       </c>
       <c r="N7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O7" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -1382,25 +1404,25 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
         <v>56</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>57</v>
       </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
       <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
         <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1418,13 +1440,16 @@
         <v>100</v>
       </c>
       <c r="N8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O8" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -1432,19 +1457,19 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
         <v>59</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>60</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>61</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>62</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -1468,13 +1493,16 @@
         <v>100</v>
       </c>
       <c r="N9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O9" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -1482,25 +1510,25 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
         <v>64</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>65</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>66</v>
       </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" t="s">
         <v>35</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1518,13 +1546,16 @@
         <v>100</v>
       </c>
       <c r="N10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O10" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -1532,25 +1563,25 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
         <v>68</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>69</v>
       </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
       <c r="G11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" t="s">
         <v>49</v>
-      </c>
-      <c r="H11" t="s">
-        <v>50</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1568,13 +1599,16 @@
         <v>100</v>
       </c>
       <c r="N11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O11" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -1582,25 +1616,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
         <v>71</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>72</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>73</v>
       </c>
-      <c r="F12" t="s">
-        <v>74</v>
-      </c>
       <c r="G12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" t="s">
         <v>35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>36</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1618,13 +1652,16 @@
         <v>100</v>
       </c>
       <c r="N12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O12" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -1632,19 +1669,19 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
         <v>75</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>76</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>77</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>78</v>
-      </c>
-      <c r="F13" t="s">
-        <v>79</v>
       </c>
       <c r="G13" t="s">
         <v>24</v>
@@ -1668,13 +1705,16 @@
         <v>100</v>
       </c>
       <c r="N13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O13" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -1682,25 +1722,25 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
         <v>80</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>81</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>82</v>
       </c>
-      <c r="F14" t="s">
-        <v>83</v>
-      </c>
       <c r="G14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" t="s">
         <v>35</v>
-      </c>
-      <c r="H14" t="s">
-        <v>36</v>
       </c>
       <c r="I14" t="s">
         <v>26</v>
@@ -1718,13 +1758,16 @@
         <v>100</v>
       </c>
       <c r="N14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O14" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
       </c>
       <c r="R14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -1732,25 +1775,25 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
         <v>84</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>85</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>86</v>
       </c>
-      <c r="F15" t="s">
-        <v>87</v>
-      </c>
       <c r="G15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" t="s">
         <v>35</v>
-      </c>
-      <c r="H15" t="s">
-        <v>36</v>
       </c>
       <c r="I15" t="s">
         <v>26</v>
@@ -1768,13 +1811,16 @@
         <v>100</v>
       </c>
       <c r="N15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O15" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -1782,25 +1828,25 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
         <v>84</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>85</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>86</v>
       </c>
-      <c r="F16" t="s">
-        <v>87</v>
-      </c>
       <c r="G16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" t="s">
         <v>49</v>
-      </c>
-      <c r="H16" t="s">
-        <v>50</v>
       </c>
       <c r="I16" t="s">
         <v>26</v>
@@ -1818,13 +1864,16 @@
         <v>100</v>
       </c>
       <c r="N16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O16" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -1832,25 +1881,25 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" t="s">
         <v>88</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>89</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>90</v>
       </c>
-      <c r="F17" t="s">
-        <v>91</v>
-      </c>
       <c r="G17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" t="s">
         <v>35</v>
-      </c>
-      <c r="H17" t="s">
-        <v>36</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
@@ -1868,13 +1917,16 @@
         <v>100</v>
       </c>
       <c r="N17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O17" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -1882,25 +1934,25 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" t="s">
         <v>92</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>93</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>94</v>
       </c>
-      <c r="F18" t="s">
-        <v>95</v>
-      </c>
       <c r="G18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" t="s">
         <v>35</v>
-      </c>
-      <c r="H18" t="s">
-        <v>36</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
@@ -1918,13 +1970,16 @@
         <v>100</v>
       </c>
       <c r="N18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O18" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -1932,25 +1987,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" t="s">
         <v>96</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>97</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>98</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>99</v>
       </c>
-      <c r="F19" t="s">
-        <v>100</v>
-      </c>
       <c r="G19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" t="s">
         <v>35</v>
-      </c>
-      <c r="H19" t="s">
-        <v>36</v>
       </c>
       <c r="I19" t="s">
         <v>26</v>
@@ -1968,13 +2023,16 @@
         <v>100</v>
       </c>
       <c r="N19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O19" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -1982,25 +2040,25 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" t="s">
         <v>101</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>102</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>103</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>104</v>
       </c>
-      <c r="F20" t="s">
-        <v>105</v>
-      </c>
       <c r="G20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" t="s">
         <v>49</v>
-      </c>
-      <c r="H20" t="s">
-        <v>50</v>
       </c>
       <c r="I20" t="s">
         <v>26</v>
@@ -2018,13 +2076,16 @@
         <v>100</v>
       </c>
       <c r="N20" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O20" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
       </c>
       <c r="R20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -2032,25 +2093,25 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" t="s">
         <v>106</v>
       </c>
-      <c r="C21" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>107</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>108</v>
       </c>
-      <c r="F21" t="s">
-        <v>109</v>
-      </c>
       <c r="G21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" t="s">
         <v>35</v>
-      </c>
-      <c r="H21" t="s">
-        <v>36</v>
       </c>
       <c r="I21" t="s">
         <v>26</v>
@@ -2068,13 +2129,16 @@
         <v>100</v>
       </c>
       <c r="N21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O21" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
       </c>
       <c r="R21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -2082,25 +2146,25 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
         <v>110</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>111</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>112</v>
       </c>
-      <c r="F22" t="s">
-        <v>113</v>
-      </c>
       <c r="G22" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" t="s">
         <v>35</v>
-      </c>
-      <c r="H22" t="s">
-        <v>36</v>
       </c>
       <c r="I22" t="s">
         <v>26</v>
@@ -2118,13 +2182,16 @@
         <v>100</v>
       </c>
       <c r="N22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O22" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
       </c>
       <c r="R22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -2132,25 +2199,25 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" t="s">
         <v>114</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>115</v>
       </c>
-      <c r="F23" t="s">
-        <v>116</v>
-      </c>
       <c r="G23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" t="s">
         <v>35</v>
-      </c>
-      <c r="H23" t="s">
-        <v>36</v>
       </c>
       <c r="I23" t="s">
         <v>26</v>
@@ -2168,13 +2235,16 @@
         <v>100</v>
       </c>
       <c r="N23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O23" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
       </c>
       <c r="R23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -2182,25 +2252,25 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" t="s">
         <v>117</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>118</v>
       </c>
-      <c r="F24" t="s">
-        <v>119</v>
-      </c>
       <c r="G24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" t="s">
         <v>35</v>
-      </c>
-      <c r="H24" t="s">
-        <v>36</v>
       </c>
       <c r="I24" t="s">
         <v>26</v>
@@ -2218,13 +2288,16 @@
         <v>100</v>
       </c>
       <c r="N24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O24" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -2232,25 +2305,25 @@
         <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" t="s">
         <v>120</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>121</v>
       </c>
-      <c r="F25" t="s">
-        <v>122</v>
-      </c>
       <c r="G25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" t="s">
         <v>35</v>
-      </c>
-      <c r="H25" t="s">
-        <v>36</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -2268,13 +2341,16 @@
         <v>100</v>
       </c>
       <c r="N25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O25" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -2282,25 +2358,25 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
         <v>123</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>124</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>125</v>
       </c>
-      <c r="F26" t="s">
-        <v>126</v>
-      </c>
       <c r="G26" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" t="s">
         <v>35</v>
-      </c>
-      <c r="H26" t="s">
-        <v>36</v>
       </c>
       <c r="I26" t="s">
         <v>26</v>
@@ -2318,13 +2394,16 @@
         <v>100</v>
       </c>
       <c r="N26" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O26" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
       </c>
       <c r="R26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -2332,25 +2411,25 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" t="s">
         <v>127</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>128</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>129</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>130</v>
       </c>
-      <c r="F27" t="s">
-        <v>131</v>
-      </c>
       <c r="G27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H27" t="s">
         <v>35</v>
-      </c>
-      <c r="H27" t="s">
-        <v>36</v>
       </c>
       <c r="I27" t="s">
         <v>26</v>
@@ -2368,13 +2447,16 @@
         <v>100</v>
       </c>
       <c r="N27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O27" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
       </c>
       <c r="R27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -2382,25 +2464,25 @@
         <v>18</v>
       </c>
       <c r="B28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" t="s">
         <v>132</v>
       </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>133</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>134</v>
       </c>
-      <c r="F28" t="s">
-        <v>135</v>
-      </c>
       <c r="G28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" t="s">
         <v>35</v>
-      </c>
-      <c r="H28" t="s">
-        <v>36</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
@@ -2418,13 +2500,16 @@
         <v>100</v>
       </c>
       <c r="N28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O28" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
       </c>
       <c r="R28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -2432,25 +2517,25 @@
         <v>18</v>
       </c>
       <c r="B29" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" t="s">
         <v>136</v>
       </c>
-      <c r="C29" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>137</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>138</v>
       </c>
-      <c r="F29" t="s">
-        <v>139</v>
-      </c>
       <c r="G29" t="s">
+        <v>41</v>
+      </c>
+      <c r="H29" t="s">
         <v>42</v>
-      </c>
-      <c r="H29" t="s">
-        <v>43</v>
       </c>
       <c r="I29" t="s">
         <v>26</v>
@@ -2468,13 +2553,16 @@
         <v>100</v>
       </c>
       <c r="N29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O29" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
       </c>
       <c r="R29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -2482,25 +2570,25 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" t="s">
         <v>136</v>
       </c>
-      <c r="C30" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>137</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>138</v>
       </c>
-      <c r="F30" t="s">
-        <v>139</v>
-      </c>
       <c r="G30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" t="s">
         <v>49</v>
-      </c>
-      <c r="H30" t="s">
-        <v>50</v>
       </c>
       <c r="I30" t="s">
         <v>26</v>
@@ -2518,13 +2606,16 @@
         <v>100</v>
       </c>
       <c r="N30" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O30" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
@@ -2532,25 +2623,25 @@
         <v>18</v>
       </c>
       <c r="B31" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" t="s">
         <v>140</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>141</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>142</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>143</v>
       </c>
-      <c r="F31" t="s">
-        <v>144</v>
-      </c>
       <c r="G31" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" t="s">
         <v>35</v>
-      </c>
-      <c r="H31" t="s">
-        <v>36</v>
       </c>
       <c r="I31" t="s">
         <v>26</v>
@@ -2568,13 +2659,16 @@
         <v>100</v>
       </c>
       <c r="N31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O31" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
       </c>
       <c r="R31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
@@ -2582,25 +2676,25 @@
         <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32" t="s">
         <v>145</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>146</v>
       </c>
-      <c r="F32" t="s">
-        <v>147</v>
-      </c>
       <c r="G32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H32" t="s">
         <v>49</v>
-      </c>
-      <c r="H32" t="s">
-        <v>50</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
@@ -2618,13 +2712,16 @@
         <v>100</v>
       </c>
       <c r="N32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O32" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P32">
+        <v>1</v>
       </c>
       <c r="R32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
@@ -2632,25 +2729,25 @@
         <v>18</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" t="s">
         <v>148</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>149</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>150</v>
       </c>
-      <c r="F33" t="s">
-        <v>151</v>
-      </c>
       <c r="G33" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" t="s">
         <v>35</v>
-      </c>
-      <c r="H33" t="s">
-        <v>36</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
@@ -2668,13 +2765,16 @@
         <v>100</v>
       </c>
       <c r="N33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O33" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P33">
+        <v>1</v>
       </c>
       <c r="R33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
@@ -2682,25 +2782,25 @@
         <v>18</v>
       </c>
       <c r="B34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" t="s">
         <v>152</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>153</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>154</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>155</v>
       </c>
-      <c r="F34" t="s">
-        <v>156</v>
-      </c>
       <c r="G34" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" t="s">
         <v>35</v>
-      </c>
-      <c r="H34" t="s">
-        <v>36</v>
       </c>
       <c r="I34" t="s">
         <v>26</v>
@@ -2718,13 +2818,16 @@
         <v>100</v>
       </c>
       <c r="N34" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O34" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P34">
+        <v>1</v>
       </c>
       <c r="R34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
@@ -2732,25 +2835,25 @@
         <v>18</v>
       </c>
       <c r="B35" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" t="s">
         <v>157</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>158</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>159</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>160</v>
       </c>
-      <c r="F35" t="s">
-        <v>161</v>
-      </c>
       <c r="G35" t="s">
+        <v>48</v>
+      </c>
+      <c r="H35" t="s">
         <v>49</v>
-      </c>
-      <c r="H35" t="s">
-        <v>50</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
@@ -2768,13 +2871,16 @@
         <v>100</v>
       </c>
       <c r="N35" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O35" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
@@ -2782,25 +2888,25 @@
         <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" t="s">
         <v>162</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>163</v>
       </c>
-      <c r="F36" t="s">
-        <v>164</v>
-      </c>
       <c r="G36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" t="s">
         <v>35</v>
-      </c>
-      <c r="H36" t="s">
-        <v>36</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
@@ -2818,13 +2924,16 @@
         <v>100</v>
       </c>
       <c r="N36" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O36" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P36">
+        <v>1</v>
       </c>
       <c r="R36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
@@ -2832,25 +2941,25 @@
         <v>18</v>
       </c>
       <c r="B37" t="s">
+        <v>164</v>
+      </c>
+      <c r="C37" t="s">
         <v>165</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>166</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>167</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>168</v>
       </c>
-      <c r="F37" t="s">
-        <v>169</v>
-      </c>
       <c r="G37" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" t="s">
         <v>35</v>
-      </c>
-      <c r="H37" t="s">
-        <v>36</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
@@ -2868,13 +2977,16 @@
         <v>100</v>
       </c>
       <c r="N37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O37" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
       </c>
       <c r="R37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
@@ -2882,25 +2994,25 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
+        <v>164</v>
+      </c>
+      <c r="C38" t="s">
         <v>165</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>166</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>167</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>168</v>
       </c>
-      <c r="F38" t="s">
-        <v>169</v>
-      </c>
       <c r="G38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38" t="s">
         <v>49</v>
-      </c>
-      <c r="H38" t="s">
-        <v>50</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
@@ -2918,13 +3030,16 @@
         <v>100</v>
       </c>
       <c r="N38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O38" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P38">
+        <v>1</v>
       </c>
       <c r="R38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
@@ -2932,25 +3047,25 @@
         <v>18</v>
       </c>
       <c r="B39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" t="s">
         <v>170</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>171</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>172</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>173</v>
       </c>
-      <c r="F39" t="s">
-        <v>174</v>
-      </c>
       <c r="G39" t="s">
+        <v>41</v>
+      </c>
+      <c r="H39" t="s">
         <v>42</v>
-      </c>
-      <c r="H39" t="s">
-        <v>43</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
@@ -2968,13 +3083,16 @@
         <v>100</v>
       </c>
       <c r="N39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O39" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P39">
+        <v>1</v>
       </c>
       <c r="R39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
@@ -2982,25 +3100,25 @@
         <v>18</v>
       </c>
       <c r="B40" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" t="s">
         <v>175</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>176</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>177</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>178</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>179</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>180</v>
-      </c>
-      <c r="H40" t="s">
-        <v>181</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
@@ -3018,13 +3136,16 @@
         <v>100</v>
       </c>
       <c r="N40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O40" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P40">
+        <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
@@ -3032,25 +3153,25 @@
         <v>18</v>
       </c>
       <c r="B41" t="s">
+        <v>181</v>
+      </c>
+      <c r="C41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" t="s">
         <v>182</v>
       </c>
-      <c r="C41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>183</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>184</v>
       </c>
-      <c r="F41" t="s">
-        <v>185</v>
-      </c>
       <c r="G41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" t="s">
         <v>35</v>
-      </c>
-      <c r="H41" t="s">
-        <v>36</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -3068,13 +3189,16 @@
         <v>100</v>
       </c>
       <c r="N41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O41" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P41">
+        <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.3">
@@ -3082,25 +3206,25 @@
         <v>18</v>
       </c>
       <c r="B42" t="s">
+        <v>185</v>
+      </c>
+      <c r="C42" t="s">
         <v>186</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>187</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>188</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>189</v>
       </c>
-      <c r="F42" t="s">
-        <v>190</v>
-      </c>
       <c r="G42" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" t="s">
         <v>35</v>
-      </c>
-      <c r="H42" t="s">
-        <v>36</v>
       </c>
       <c r="I42" t="s">
         <v>26</v>
@@ -3118,13 +3242,16 @@
         <v>100</v>
       </c>
       <c r="N42" t="s">
-        <v>27</v>
+        <v>211</v>
       </c>
       <c r="O42" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-20.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-20.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -919,19 +919,19 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -3353,19 +3353,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -3762,19 +3762,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x2</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S41" t="n">
